--- a/public/downloads/FesterEdge2017.xlsx
+++ b/public/downloads/FesterEdge2017.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="55">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -167,10 +169,31 @@
     <t>Adsorbate_name</t>
   </si>
   <si>
-    <t>O</t>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>HO</t>
+  </si>
+  <si>
+    <t>O</t>
   </si>
   <si>
     <t>HO2</t>
@@ -659,10 +682,10 @@
         <v>16</v>
       </c>
       <c r="N3" s="5">
-        <v>98.24680066108704</v>
+        <v>98246.80066108704</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03346280676467542</v>
+        <v>33.46280676467542</v>
       </c>
       <c r="P3" s="5">
         <v>2936</v>
@@ -709,10 +732,10 @@
         <v>16</v>
       </c>
       <c r="N4" s="5">
-        <v>182.1334140300751</v>
+        <v>182133.4140300751</v>
       </c>
       <c r="O4" s="4">
-        <v>0.05959863024544342</v>
+        <v>59.59863024544342</v>
       </c>
       <c r="P4" s="5">
         <v>3056</v>
@@ -759,10 +782,10 @@
         <v>16</v>
       </c>
       <c r="N5" s="5">
-        <v>436.6573843955994</v>
+        <v>436657.3843955994</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1850243154218641</v>
+        <v>185.0243154218641</v>
       </c>
       <c r="P5" s="5">
         <v>2360</v>
@@ -809,10 +832,10 @@
         <v>16</v>
       </c>
       <c r="N6" s="5">
-        <v>263.0655422210693</v>
+        <v>263065.5422210693</v>
       </c>
       <c r="O6" s="4">
-        <v>0.0860253571684334</v>
+        <v>86.0253571684334</v>
       </c>
       <c r="P6" s="5">
         <v>3058</v>
@@ -859,10 +882,10 @@
         <v>16</v>
       </c>
       <c r="N7" s="5">
-        <v>683.3702547550201</v>
+        <v>683370.2547550201</v>
       </c>
       <c r="O7" s="4">
-        <v>0.242243975453747</v>
+        <v>242.243975453747</v>
       </c>
       <c r="P7" s="5">
         <v>2821</v>
@@ -909,10 +932,10 @@
         <v>16</v>
       </c>
       <c r="N8" s="5">
-        <v>40.96730756759644</v>
+        <v>40967.30756759644</v>
       </c>
       <c r="O8" s="4">
-        <v>0.0161798213142166</v>
+        <v>16.1798213142166</v>
       </c>
       <c r="P8" s="5">
         <v>2532</v>
@@ -959,10 +982,10 @@
         <v>16</v>
       </c>
       <c r="N9" s="5">
-        <v>82.59043741226196</v>
+        <v>82590.43741226196</v>
       </c>
       <c r="O9" s="4">
-        <v>0.03101405835984302</v>
+        <v>31.01405835984302</v>
       </c>
       <c r="P9" s="5">
         <v>2663</v>
@@ -1009,10 +1032,10 @@
         <v>16</v>
       </c>
       <c r="N10" s="5">
-        <v>219.8974440097809</v>
+        <v>219897.4440097809</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08579689582902103</v>
+        <v>85.79689582902103</v>
       </c>
       <c r="P10" s="5">
         <v>2563</v>
@@ -1059,10 +1082,10 @@
         <v>16</v>
       </c>
       <c r="N11" s="5">
-        <v>101.4463288784027</v>
+        <v>101446.3288784027</v>
       </c>
       <c r="O11" s="4">
-        <v>0.04009736319304455</v>
+        <v>40.09736319304455</v>
       </c>
       <c r="P11" s="5">
         <v>2530</v>
@@ -1109,10 +1132,10 @@
         <v>16</v>
       </c>
       <c r="N12" s="5">
-        <v>51.57299900054932</v>
+        <v>51572.99900054932</v>
       </c>
       <c r="O12" s="4">
-        <v>0.02187150084840938</v>
+        <v>21.87150084840938</v>
       </c>
       <c r="P12" s="5">
         <v>2358</v>
@@ -1159,10 +1182,10 @@
         <v>16</v>
       </c>
       <c r="N13" s="5">
-        <v>214.8220586776733</v>
+        <v>214822.0586776733</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07628624242815105</v>
+        <v>76.28624242815104</v>
       </c>
       <c r="P13" s="5">
         <v>2816</v>
@@ -1209,10 +1232,10 @@
         <v>16</v>
       </c>
       <c r="N14" s="5">
-        <v>1189.207078695297</v>
+        <v>1189207.078695297</v>
       </c>
       <c r="O14" s="4">
-        <v>0.3350822988715969</v>
+        <v>335.0822988715968</v>
       </c>
       <c r="P14" s="5">
         <v>3549</v>
@@ -1259,10 +1282,10 @@
         <v>16</v>
       </c>
       <c r="N15" s="5">
-        <v>863.1414713859558</v>
+        <v>863141.4713859558</v>
       </c>
       <c r="O15" s="4">
-        <v>0.3301994917314292</v>
+        <v>330.1994917314291</v>
       </c>
       <c r="P15" s="5">
         <v>2614</v>
@@ -1309,10 +1332,10 @@
         <v>16</v>
       </c>
       <c r="N16" s="5">
-        <v>354.5943946838379</v>
+        <v>354594.3946838379</v>
       </c>
       <c r="O16" s="4">
-        <v>0.1018364143262027</v>
+        <v>101.8364143262027</v>
       </c>
       <c r="P16" s="5">
         <v>3482</v>
@@ -1359,10 +1382,10 @@
         <v>16</v>
       </c>
       <c r="N17" s="5">
-        <v>317.6105237007141</v>
+        <v>317610.5237007141</v>
       </c>
       <c r="O17" s="4">
-        <v>0.09919129409766213</v>
+        <v>99.19129409766212</v>
       </c>
       <c r="P17" s="5">
         <v>3202</v>
@@ -1390,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1401,9 +1424,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1437,8 +1466,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1460,107 +1497,161 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3853363086783852</v>
+        <v>0.6620017616691977</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2894090896619387</v>
+        <v>0.6620017616691977</v>
       </c>
       <c r="D3" s="4">
-        <v>0.348713249180117</v>
+        <v>0.6401892247868565</v>
       </c>
       <c r="E3" s="4">
-        <v>88.19727891156464</v>
+        <v>87.34693877551021</v>
       </c>
       <c r="F3" s="4">
-        <v>86.890380313199</v>
+        <v>87.26510067114094</v>
       </c>
       <c r="G3" s="5">
         <v>6</v>
       </c>
       <c r="H3" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.6620017616691977</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4121541910309108</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4121541910309108</v>
+      </c>
+      <c r="R3" s="5">
+        <v>6</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5086984676185059</v>
+        <v>0.7103279699472679</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4827330838479668</v>
+        <v>0.7103279699472679</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4608262483725743</v>
+        <v>0.6944460328723894</v>
       </c>
       <c r="E4" s="4">
-        <v>88.18027210884355</v>
+        <v>86.22448979591837</v>
       </c>
       <c r="F4" s="4">
-        <v>87.10104399701704</v>
+        <v>87.57270693512309</v>
       </c>
       <c r="G4" s="5">
         <v>6</v>
       </c>
       <c r="H4" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.6152980409050129</v>
+      </c>
+      <c r="O4" s="5">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.499095761554517</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.499095761554517</v>
+      </c>
+      <c r="R4" s="5">
+        <v>6</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4320053357229439</v>
+        <v>0.6545672069628257</v>
       </c>
       <c r="C5" s="4">
-        <v>0.5309712858452258</v>
+        <v>0.8476553306344196</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4458114178286663</v>
+        <v>0.7908114537366648</v>
       </c>
       <c r="E5" s="4">
-        <v>88.56292517006803</v>
+        <v>82.88265306122449</v>
       </c>
       <c r="F5" s="4">
-        <v>76.70581655480981</v>
+        <v>69.17785234899328</v>
       </c>
       <c r="G5" s="5">
         <v>4</v>
@@ -1583,9 +1674,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.6545672069628257</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.8476553306344196</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1596,6 +1703,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1603,7 +1711,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1614,9 +1722,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1650,8 +1764,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1673,116 +1795,170 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5450975357128982</v>
+        <v>0.9800526006119696</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4749518539941505</v>
+        <v>0.9800526006119696</v>
       </c>
       <c r="D3" s="4">
-        <v>0.5025760589672927</v>
+        <v>0.9507936341660468</v>
       </c>
       <c r="E3" s="4">
-        <v>86.21882086167797</v>
+        <v>83.29931972789116</v>
       </c>
       <c r="F3" s="4">
-        <v>85.04101416853234</v>
+        <v>85.72147651006711</v>
       </c>
       <c r="G3" s="5">
         <v>6</v>
       </c>
       <c r="H3" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.9800526006119696</v>
+      </c>
+      <c r="O3" s="5">
+        <v>6</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5885476261458299</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5885476261458299</v>
+      </c>
+      <c r="R3" s="5">
+        <v>6</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5698054336604722</v>
+        <v>1.039465770983081</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5409250937880756</v>
+        <v>0.7350286731250151</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5268559160925198</v>
+        <v>1.033405647539477</v>
       </c>
       <c r="E4" s="4">
-        <v>86.30385487528341</v>
+        <v>81.64965986394557</v>
       </c>
       <c r="F4" s="4">
-        <v>85.13795674869642</v>
+        <v>82.99589858314683</v>
       </c>
       <c r="G4" s="5">
         <v>6</v>
       </c>
       <c r="H4" s="5">
+        <v>4</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>2</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>1</v>
+      </c>
+      <c r="M4" s="5">
+        <v>1</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.9941847399101675</v>
+      </c>
+      <c r="O4" s="5">
         <v>5</v>
       </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>1</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>1</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="P4" s="4">
+        <v>0.5591353421354105</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.616625173274997</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.550301987050787</v>
+        <v>0.9290913678515693</v>
       </c>
       <c r="C5" s="4">
-        <v>0.8170417466259892</v>
+        <v>1.115376267454432</v>
       </c>
       <c r="D5" s="4">
-        <v>0.5339273549426338</v>
+        <v>0.9866067506182929</v>
       </c>
       <c r="E5" s="4">
-        <v>83.9455782312925</v>
+        <v>79.37074829931974</v>
       </c>
       <c r="F5" s="4">
-        <v>72.98378076062639</v>
+        <v>77.20357941834452</v>
       </c>
       <c r="G5" s="5">
         <v>4</v>
       </c>
       <c r="H5" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -1796,9 +1972,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.9290913678515693</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>1.115376267454432</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1809,6 +2001,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1816,7 +2009,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1827,9 +2020,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1863,8 +2062,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1886,25 +2093,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3122283572306325</v>
+        <v>0.5086984676185059</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2781698009665547</v>
+        <v>0.4827330838479668</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2526663099080413</v>
+        <v>0.4608262483725743</v>
       </c>
       <c r="E3" s="4">
-        <v>91.12811791383221</v>
+        <v>88.18027210884355</v>
       </c>
       <c r="F3" s="4">
-        <v>87.46644295301974</v>
+        <v>87.10104399701704</v>
       </c>
       <c r="G3" s="5">
         <v>6</v>
@@ -1927,25 +2152,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.4827330838479668</v>
+      </c>
+      <c r="O3" s="5">
+        <v>5</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3710834786934782</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.414141713907527</v>
+      </c>
+      <c r="R3" s="5">
+        <v>5</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2680449149963333</v>
+        <v>0.3853363086783852</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2890740547193559</v>
+        <v>0.2894090896619387</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2301558509657771</v>
+        <v>0.348713249180117</v>
       </c>
       <c r="E4" s="4">
-        <v>91.43990929705217</v>
+        <v>88.19727891156464</v>
       </c>
       <c r="F4" s="4">
-        <v>87.59321401938817</v>
+        <v>86.890380313199</v>
       </c>
       <c r="G4" s="5">
         <v>6</v>
@@ -1968,25 +2211,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.2863111647192282</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3022738045837818</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2469963176922603</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2982115329492245</v>
+        <v>0.4320053357229439</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2613701378420122</v>
+        <v>0.5309712858452258</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1366264573220946</v>
+        <v>0.4458114178286663</v>
       </c>
       <c r="E5" s="4">
-        <v>89.12414965986393</v>
+        <v>88.56292517006803</v>
       </c>
       <c r="F5" s="4">
-        <v>76.33668903803131</v>
+        <v>76.70581655480981</v>
       </c>
       <c r="G5" s="5">
         <v>4</v>
@@ -2009,9 +2270,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4320053357229439</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.5309712858452258</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2022,6 +2299,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2029,7 +2307,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2040,9 +2318,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2076,8 +2360,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2099,25 +2391,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4072893415242523</v>
+        <v>0.5698054336604722</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3066133281882344</v>
+        <v>0.5409250937880756</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3358518237223317</v>
+        <v>0.5268559160925198</v>
       </c>
       <c r="E3" s="4">
-        <v>85.62925170068029</v>
+        <v>86.30385487528341</v>
       </c>
       <c r="F3" s="4">
-        <v>82.46085011185696</v>
+        <v>85.13795674869642</v>
       </c>
       <c r="G3" s="5">
         <v>6</v>
@@ -2140,25 +2450,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.5409250937880756</v>
+      </c>
+      <c r="O3" s="5">
+        <v>5</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.308452207851559</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3354862415749949</v>
+      </c>
+      <c r="R3" s="5">
+        <v>5</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3848122745833298</v>
+        <v>0.5450975357128982</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3774754114312714</v>
+        <v>0.4749518539941505</v>
       </c>
       <c r="D4" s="4">
-        <v>0.322154600429684</v>
+        <v>0.5025760589672927</v>
       </c>
       <c r="E4" s="4">
-        <v>86.39455782312926</v>
+        <v>86.21882086167797</v>
       </c>
       <c r="F4" s="4">
-        <v>83.51789709172274</v>
+        <v>85.04101416853234</v>
       </c>
       <c r="G4" s="5">
         <v>6</v>
@@ -2181,25 +2509,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.4749518539941505</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2338310700520841</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1964224660000036</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4310164035546933</v>
+        <v>0.550301987050787</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4171196141339237</v>
+        <v>0.8170417466259892</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3043523779992796</v>
+        <v>0.5339273549426338</v>
       </c>
       <c r="E5" s="4">
-        <v>84.29421768707482</v>
+        <v>83.9455782312925</v>
       </c>
       <c r="F5" s="4">
-        <v>68.46476510067114</v>
+        <v>72.98378076062639</v>
       </c>
       <c r="G5" s="5">
         <v>4</v>
@@ -2222,9 +2568,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.550301987050787</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.8170417466259892</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2235,6 +2597,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2242,7 +2605,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2253,9 +2616,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2289,8 +2658,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2312,107 +2689,161 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.207837047441113</v>
+        <v>0.2680449149963333</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2157230138447431</v>
+        <v>0.2890740547193559</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3605384394054269</v>
+        <v>0.2301558509657771</v>
       </c>
       <c r="E3" s="4">
-        <v>56.87074829931969</v>
+        <v>91.43990929705217</v>
       </c>
       <c r="F3" s="4">
-        <v>56.18568232662172</v>
+        <v>87.59321401938817</v>
       </c>
       <c r="G3" s="5">
         <v>6</v>
       </c>
       <c r="H3" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.2844169818343403</v>
+      </c>
+      <c r="O3" s="5">
+        <v>5</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2665810137838491</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2955936634499949</v>
+      </c>
+      <c r="R3" s="5">
+        <v>5</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.7910061490493471</v>
+        <v>0.3122283572306325</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5207418663139644</v>
+        <v>0.2781698009665547</v>
       </c>
       <c r="D4" s="4">
-        <v>0.8815420232174583</v>
+        <v>0.2526663099080413</v>
       </c>
       <c r="E4" s="4">
-        <v>57.2335600907029</v>
+        <v>91.12811791383221</v>
       </c>
       <c r="F4" s="4">
-        <v>58.51603281133472</v>
+        <v>87.46644295301974</v>
       </c>
       <c r="G4" s="5">
         <v>6</v>
       </c>
       <c r="H4" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.2516220238244727</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.185332026269532</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1762186085781286</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4885880531061733</v>
+        <v>0.2982115329492245</v>
       </c>
       <c r="C5" s="4">
-        <v>0.5527585677440113</v>
+        <v>0.2613701378420122</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4256410690161121</v>
+        <v>0.1366264573220946</v>
       </c>
       <c r="E5" s="4">
-        <v>63.69897959183673</v>
+        <v>89.12414965986393</v>
       </c>
       <c r="F5" s="4">
-        <v>69.58892617449665</v>
+        <v>76.33668903803131</v>
       </c>
       <c r="G5" s="5">
         <v>4</v>
@@ -2421,23 +2852,39 @@
         <v>3</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2982115329492245</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2613701378420122</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2448,6 +2895,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2455,7 +2903,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2466,9 +2914,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2502,8 +2956,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2525,25 +2987,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2522935022144773</v>
+        <v>0.3848122745833298</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1535232916623976</v>
+        <v>0.3774754114312714</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2009729096517881</v>
+        <v>0.322154600429684</v>
       </c>
       <c r="E3" s="4">
-        <v>91.15646258503396</v>
+        <v>86.39455782312926</v>
       </c>
       <c r="F3" s="4">
-        <v>85.3542132736779</v>
+        <v>83.51789709172274</v>
       </c>
       <c r="G3" s="5">
         <v>6</v>
@@ -2566,25 +3046,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1800077639998676</v>
+      </c>
+      <c r="O3" s="5">
+        <v>5</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3848122745833298</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4134769642312449</v>
+      </c>
+      <c r="R3" s="5">
+        <v>5</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2461901005952048</v>
+        <v>0.4072893415242523</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2843063965919669</v>
+        <v>0.3066133281882344</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2879293916607726</v>
+        <v>0.3358518237223317</v>
       </c>
       <c r="E4" s="4">
-        <v>90.0340136054421</v>
+        <v>85.62925170068029</v>
       </c>
       <c r="F4" s="4">
-        <v>79.89000745712157</v>
+        <v>82.46085011185696</v>
       </c>
       <c r="G4" s="5">
         <v>6</v>
@@ -2607,25 +3105,43 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.2563419487512306</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3109662832682299</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2422940480312537</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4679402075901873</v>
+        <v>0.4310164035546933</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2871641299630028</v>
+        <v>0.4171196141339237</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4016044400820658</v>
+        <v>0.3043523779992796</v>
       </c>
       <c r="E5" s="4">
-        <v>88.91156462585033</v>
+        <v>84.29421768707482</v>
       </c>
       <c r="F5" s="4">
-        <v>69.74832214765101</v>
+        <v>68.46476510067114</v>
       </c>
       <c r="G5" s="5">
         <v>4</v>
@@ -2648,9 +3164,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4310164035546933</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4171196141339237</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2661,6 +3193,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2668,7 +3201,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2679,9 +3212,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2715,8 +3254,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2738,25 +3285,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3497314859068103</v>
+        <v>0.7910061490493471</v>
       </c>
       <c r="C3" s="4">
-        <v>0.427887047120719</v>
+        <v>0.5207418663139644</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4284708067303271</v>
+        <v>0.8815420232174583</v>
       </c>
       <c r="E3" s="4">
-        <v>56.22448979591838</v>
+        <v>57.2335600907029</v>
       </c>
       <c r="F3" s="4">
-        <v>60.36726323639077</v>
+        <v>58.51603281133472</v>
       </c>
       <c r="G3" s="5">
         <v>6</v>
@@ -2779,25 +3344,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>3</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7910061490493471</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5207418663139644</v>
+      </c>
+      <c r="R3" s="5">
+        <v>3</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.9259209247387096</v>
+        <v>0.207837047441113</v>
       </c>
       <c r="C4" s="4">
-        <v>0.6588571730090962</v>
+        <v>0.2157230138447431</v>
       </c>
       <c r="D4" s="4">
-        <v>0.9791006805458409</v>
+        <v>0.3605384394054269</v>
       </c>
       <c r="E4" s="4">
-        <v>56.30952380952377</v>
+        <v>56.87074829931969</v>
       </c>
       <c r="F4" s="4">
-        <v>60.88366890380299</v>
+        <v>56.18568232662172</v>
       </c>
       <c r="G4" s="5">
         <v>6</v>
@@ -2820,25 +3401,41 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>3</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.207837047441113</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2157230138447431</v>
+      </c>
+      <c r="R4" s="5">
+        <v>3</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6038314880121294</v>
+        <v>0.4885880531061733</v>
       </c>
       <c r="C5" s="4">
-        <v>0.7466279896232534</v>
+        <v>0.5527585677440113</v>
       </c>
       <c r="D5" s="4">
-        <v>0.6126596721026618</v>
+        <v>0.4256410690161121</v>
       </c>
       <c r="E5" s="4">
-        <v>61.4030612244898</v>
+        <v>63.69897959183673</v>
       </c>
       <c r="F5" s="4">
-        <v>70.15659955257271</v>
+        <v>69.58892617449665</v>
       </c>
       <c r="G5" s="5">
         <v>4</v>
@@ -2861,9 +3458,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4885880531061733</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.5527585677440113</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2874,6 +3487,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2881,7 +3495,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2892,9 +3506,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,8 +3548,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2951,132 +3579,202 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3433032179816582</v>
+        <v>0.2461901005952048</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2349677705748574</v>
+        <v>0.2843063965919669</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3000290239794499</v>
+        <v>0.2879293916607726</v>
       </c>
       <c r="E3" s="4">
-        <v>84.09297052154196</v>
+        <v>90.0340136054421</v>
       </c>
       <c r="F3" s="4">
-        <v>77.43288590604206</v>
+        <v>79.89000745712157</v>
       </c>
       <c r="G3" s="5">
         <v>6</v>
       </c>
       <c r="H3" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.01870558490176109</v>
+      </c>
+      <c r="O3" s="5">
+        <v>5</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2432301996133977</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2844956323941505</v>
+      </c>
+      <c r="R3" s="5">
+        <v>5</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3509507616441283</v>
+        <v>0.2522935022144773</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4937444909561274</v>
+        <v>0.1535232916623976</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3554108132995187</v>
+        <v>0.2009729096517881</v>
       </c>
       <c r="E4" s="4">
-        <v>83.8945578231293</v>
+        <v>91.15646258503396</v>
       </c>
       <c r="F4" s="4">
-        <v>74.94034302758942</v>
+        <v>85.3542132736779</v>
       </c>
       <c r="G4" s="5">
         <v>6</v>
       </c>
       <c r="H4" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.02048430705448041</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2454653998629838</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1494264302515015</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.5672751731954104</v>
+        <v>0.4679402075901873</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3580606638565769</v>
+        <v>0.2871641299630028</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3304259173355018</v>
+        <v>0.4016044400820658</v>
       </c>
       <c r="E5" s="4">
-        <v>84.82993197278913</v>
+        <v>88.91156462585033</v>
       </c>
       <c r="F5" s="4">
-        <v>64.87136465324386</v>
+        <v>69.74832214765101</v>
       </c>
       <c r="G5" s="5">
         <v>4</v>
       </c>
       <c r="H5" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" s="5">
         <v>2</v>
       </c>
       <c r="J5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4679402075901873</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2871641299630028</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3087,12 +3785,1458 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.9259209247387096</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.6588571730090962</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.9791006805458409</v>
+      </c>
+      <c r="E3" s="4">
+        <v>56.30952380952377</v>
+      </c>
+      <c r="F3" s="4">
+        <v>60.88366890380299</v>
+      </c>
+      <c r="G3" s="5">
+        <v>6</v>
+      </c>
+      <c r="H3" s="5">
+        <v>3</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>3</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>3</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>3</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.9259209247387096</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6588571730090962</v>
+      </c>
+      <c r="R3" s="5">
+        <v>3</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.3497314859068103</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.427887047120719</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.4284708067303271</v>
+      </c>
+      <c r="E4" s="4">
+        <v>56.22448979591838</v>
+      </c>
+      <c r="F4" s="4">
+        <v>60.36726323639077</v>
+      </c>
+      <c r="G4" s="5">
+        <v>6</v>
+      </c>
+      <c r="H4" s="5">
+        <v>3</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>3</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>3</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>3</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3497314859068103</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.427887047120719</v>
+      </c>
+      <c r="R4" s="5">
+        <v>3</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.6038314880121294</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.7466279896232534</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.6126596721026618</v>
+      </c>
+      <c r="E5" s="4">
+        <v>61.4030612244898</v>
+      </c>
+      <c r="F5" s="4">
+        <v>70.15659955257271</v>
+      </c>
+      <c r="G5" s="5">
+        <v>4</v>
+      </c>
+      <c r="H5" s="5">
+        <v>3</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.6038314880121294</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.7466279896232534</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.3509507616441283</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.4937444909561274</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.3554108132995187</v>
+      </c>
+      <c r="E3" s="4">
+        <v>83.8945578231293</v>
+      </c>
+      <c r="F3" s="4">
+        <v>74.94034302758942</v>
+      </c>
+      <c r="G3" s="5">
+        <v>6</v>
+      </c>
+      <c r="H3" s="5">
+        <v>3</v>
+      </c>
+      <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5">
+        <v>2</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>2</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>3</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3509507616441283</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4937444909561274</v>
+      </c>
+      <c r="R3" s="5">
+        <v>3</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.3433032179816582</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.2349677705748574</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.3000290239794499</v>
+      </c>
+      <c r="E4" s="4">
+        <v>84.09297052154196</v>
+      </c>
+      <c r="F4" s="4">
+        <v>77.43288590604206</v>
+      </c>
+      <c r="G4" s="5">
+        <v>6</v>
+      </c>
+      <c r="H4" s="5">
+        <v>4</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>2</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>2</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>4</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3433032179816582</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2349677705748574</v>
+      </c>
+      <c r="R4" s="5">
+        <v>4</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.5672751731954104</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.3580606638565769</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.3304259173355018</v>
+      </c>
+      <c r="E5" s="4">
+        <v>84.82993197278913</v>
+      </c>
+      <c r="F5" s="4">
+        <v>64.87136465324386</v>
+      </c>
+      <c r="G5" s="5">
+        <v>4</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5">
+        <v>2</v>
+      </c>
+      <c r="J5" s="5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5672751731954104</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3580606638565769</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>75</v>
+      </c>
+      <c r="C3" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="D3" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.4213520719042947</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.4609839258365052</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.3813883386514263</v>
+      </c>
+      <c r="K3" s="4">
+        <v>86.05867346938776</v>
+      </c>
+      <c r="L3" s="4">
+        <v>78.12569910514405</v>
+      </c>
+      <c r="M3" s="5">
+        <v>16</v>
+      </c>
+      <c r="N3" s="5">
+        <v>98246.80066108704</v>
+      </c>
+      <c r="O3" s="4">
+        <v>33.46280676467542</v>
+      </c>
+      <c r="P3" s="5">
+        <v>2936</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>62.5</v>
+      </c>
+      <c r="C4" s="3">
+        <v>6.25</v>
+      </c>
+      <c r="D4" s="3">
+        <v>31.25</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>18.75</v>
+      </c>
+      <c r="G4" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="H4" s="4">
+        <v>1.02169545268967</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.7072215492323266</v>
+      </c>
+      <c r="J4" s="4">
+        <v>1.107532532265658</v>
+      </c>
+      <c r="K4" s="4">
+        <v>82.59778911564626</v>
+      </c>
+      <c r="L4" s="4">
+        <v>81.4422539149889</v>
+      </c>
+      <c r="M4" s="5">
+        <v>16</v>
+      </c>
+      <c r="N4" s="5">
+        <v>182133.4140300751</v>
+      </c>
+      <c r="O4" s="4">
+        <v>59.59863024544342</v>
+      </c>
+      <c r="P4" s="5">
+        <v>3056</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>81.25</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>18.75</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>18.75</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.2793121373985954</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.2998248654980312</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.2592520805780836</v>
+      </c>
+      <c r="K5" s="4">
+        <v>88.10799319727892</v>
+      </c>
+      <c r="L5" s="4">
+        <v>85.59354026845632</v>
+      </c>
+      <c r="M5" s="5">
+        <v>16</v>
+      </c>
+      <c r="N5" s="5">
+        <v>436657.3843955994</v>
+      </c>
+      <c r="O5" s="4">
+        <v>185.0243154218641</v>
+      </c>
+      <c r="P5" s="5">
+        <v>2360</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>81.25</v>
+      </c>
+      <c r="C6" s="3">
+        <v>6.25</v>
+      </c>
+      <c r="D6" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.3617036552461997</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.3736300050176257</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.329733471805956</v>
+      </c>
+      <c r="K6" s="4">
+        <v>82.98469387755102</v>
+      </c>
+      <c r="L6" s="4">
+        <v>82.50489373601791</v>
+      </c>
+      <c r="M6" s="5">
+        <v>16</v>
+      </c>
+      <c r="N6" s="5">
+        <v>263065.5422210693</v>
+      </c>
+      <c r="O6" s="4">
+        <v>86.0253571684334</v>
+      </c>
+      <c r="P6" s="5">
+        <v>3058</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>81.25</v>
+      </c>
+      <c r="C7" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="D7" s="3">
+        <v>6.25</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>6.25</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.3288185033912451</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.3895149195222857</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.3303927687636825</v>
+      </c>
+      <c r="K7" s="4">
+        <v>87.31930272108846</v>
+      </c>
+      <c r="L7" s="4">
+        <v>81.06613534675719</v>
+      </c>
+      <c r="M7" s="5">
+        <v>16</v>
+      </c>
+      <c r="N7" s="5">
+        <v>683370.2547550201</v>
+      </c>
+      <c r="O7" s="4">
+        <v>242.243975453747</v>
+      </c>
+      <c r="P7" s="5">
+        <v>2821</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>93.75</v>
+      </c>
+      <c r="C8" s="3">
+        <v>6.25</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.5053605339602418</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.534031047161055</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.5242694239394903</v>
+      </c>
+      <c r="K8" s="4">
+        <v>85.80994897959184</v>
+      </c>
+      <c r="L8" s="4">
+        <v>82.85864093959732</v>
+      </c>
+      <c r="M8" s="5">
+        <v>16</v>
+      </c>
+      <c r="N8" s="5">
+        <v>40967.30756759644</v>
+      </c>
+      <c r="O8" s="4">
+        <v>16.1798213142166</v>
+      </c>
+      <c r="P8" s="5">
+        <v>2532</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>87.5</v>
+      </c>
+      <c r="C9" s="3">
+        <v>6.25</v>
+      </c>
+      <c r="D9" s="3">
+        <v>6.25</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>6.25</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.6626539550683574</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.7114671732580901</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.6483672581574993</v>
+      </c>
+      <c r="K9" s="4">
+        <v>81.69855442176872</v>
+      </c>
+      <c r="L9" s="4">
+        <v>82.56991051454138</v>
+      </c>
+      <c r="M9" s="5">
+        <v>16</v>
+      </c>
+      <c r="N9" s="5">
+        <v>82590.43741226196</v>
+      </c>
+      <c r="O9" s="4">
+        <v>31.01405835984302</v>
+      </c>
+      <c r="P9" s="5">
+        <v>2663</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>81.25</v>
+      </c>
+      <c r="C10" s="3">
+        <v>6.25</v>
+      </c>
+      <c r="D10" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.3605103151597085</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.3768156935026626</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.3359523721648084</v>
+      </c>
+      <c r="K10" s="4">
+        <v>88.28231292517007</v>
+      </c>
+      <c r="L10" s="4">
+        <v>84.42323825503352</v>
+      </c>
+      <c r="M10" s="5">
+        <v>16</v>
+      </c>
+      <c r="N10" s="5">
+        <v>219897.4440097809</v>
+      </c>
+      <c r="O10" s="4">
+        <v>85.79689582902103</v>
+      </c>
+      <c r="P10" s="5">
+        <v>2563</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>75</v>
+      </c>
+      <c r="C11" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="D11" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.3409317259765629</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.3578022525939142</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.2947778095413227</v>
+      </c>
+      <c r="K11" s="4">
+        <v>85.68239795918367</v>
+      </c>
+      <c r="L11" s="4">
+        <v>82.06305928411631</v>
+      </c>
+      <c r="M11" s="5">
+        <v>16</v>
+      </c>
+      <c r="N11" s="5">
+        <v>101446.3288784027</v>
+      </c>
+      <c r="O11" s="4">
+        <v>40.09736319304455</v>
+      </c>
+      <c r="P11" s="5">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>81.25</v>
+      </c>
+      <c r="C12" s="3">
+        <v>6.25</v>
+      </c>
+      <c r="D12" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.2440202732573241</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.2417824441282042</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.2022485675677047</v>
+      </c>
+      <c r="K12" s="4">
+        <v>90.74404761904761</v>
+      </c>
+      <c r="L12" s="4">
+        <v>84.73154362416108</v>
+      </c>
+      <c r="M12" s="5">
+        <v>16</v>
+      </c>
+      <c r="N12" s="5">
+        <v>51572.99900054932</v>
+      </c>
+      <c r="O12" s="4">
+        <v>21.87150084840938</v>
+      </c>
+      <c r="P12" s="5">
+        <v>2358</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>75</v>
+      </c>
+      <c r="C13" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="D13" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.3686710600830082</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.3427578574650283</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.2927442538093586</v>
+      </c>
+      <c r="K13" s="4">
+        <v>85.58248299319727</v>
+      </c>
+      <c r="L13" s="4">
+        <v>79.35822147651007</v>
+      </c>
+      <c r="M13" s="5">
+        <v>16</v>
+      </c>
+      <c r="N13" s="5">
+        <v>214822.0586776733</v>
+      </c>
+      <c r="O13" s="4">
+        <v>76.28624242815104</v>
+      </c>
+      <c r="P13" s="5">
+        <v>2816</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>56.25</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>43.75</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>43.75</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.4967132119604659</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.4297411493009063</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.5721904407376099</v>
+      </c>
+      <c r="K14" s="4">
+        <v>58.71386054421768</v>
+      </c>
+      <c r="L14" s="4">
+        <v>60.41037472035792</v>
+      </c>
+      <c r="M14" s="5">
+        <v>16</v>
+      </c>
+      <c r="N14" s="5">
+        <v>1189207.078695297</v>
+      </c>
+      <c r="O14" s="4">
+        <v>335.0822988715968</v>
+      </c>
+      <c r="P14" s="5">
+        <v>3549</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>75</v>
+      </c>
+      <c r="C15" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="D15" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.3002459017011899</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.2286615477628555</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.2833176093083973</v>
+      </c>
+      <c r="K15" s="4">
+        <v>90.17431972789115</v>
+      </c>
+      <c r="L15" s="4">
+        <v>79.40366331096197</v>
+      </c>
+      <c r="M15" s="5">
+        <v>16</v>
+      </c>
+      <c r="N15" s="5">
+        <v>863141.4713859558</v>
+      </c>
+      <c r="O15" s="4">
+        <v>330.1994917314291</v>
+      </c>
+      <c r="P15" s="5">
+        <v>2614</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>56.25</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3">
+        <v>43.75</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>43.75</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.6293275259951023</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.6111240699176895</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.6810042257542284</v>
+      </c>
+      <c r="K16" s="4">
+        <v>57.55102040816327</v>
+      </c>
+      <c r="L16" s="4">
+        <v>63.00824944071597</v>
+      </c>
+      <c r="M16" s="5">
+        <v>16</v>
+      </c>
+      <c r="N16" s="5">
+        <v>354594.3946838379</v>
+      </c>
+      <c r="O16" s="4">
+        <v>101.8364143262027</v>
+      </c>
+      <c r="P16" s="5">
+        <v>3482</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>50</v>
+      </c>
+      <c r="C17" s="3">
+        <v>18.75</v>
+      </c>
+      <c r="D17" s="3">
+        <v>31.25</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>31.25</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.4021640356585225</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.3473956523780486</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.3283964183134886</v>
+      </c>
+      <c r="K17" s="4">
+        <v>84.20280612244896</v>
+      </c>
+      <c r="L17" s="4">
+        <v>73.35780201342425</v>
+      </c>
+      <c r="M17" s="5">
+        <v>16</v>
+      </c>
+      <c r="N17" s="5">
+        <v>317610.5237007141</v>
+      </c>
+      <c r="O17" s="4">
+        <v>99.19129409766212</v>
+      </c>
+      <c r="P17" s="5">
+        <v>3202</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3847,9 +5991,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>12</v>
+      </c>
+      <c r="C3" s="5">
+        <v>2</v>
+      </c>
+      <c r="D3" s="5">
+        <v>2</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>2</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>10</v>
+      </c>
+      <c r="C4" s="5">
+        <v>1</v>
+      </c>
+      <c r="D4" s="5">
+        <v>5</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>3</v>
+      </c>
+      <c r="G4" s="5">
+        <v>2</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>1</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>13</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>3</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>3</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>13</v>
+      </c>
+      <c r="C6" s="5">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5">
+        <v>2</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>2</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>13</v>
+      </c>
+      <c r="C7" s="5">
+        <v>2</v>
+      </c>
+      <c r="D7" s="5">
+        <v>1</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>15</v>
+      </c>
+      <c r="C8" s="5">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>14</v>
+      </c>
+      <c r="C9" s="5">
+        <v>1</v>
+      </c>
+      <c r="D9" s="5">
+        <v>1</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>1</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>1</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>13</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5">
+        <v>2</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>2</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>12</v>
+      </c>
+      <c r="C11" s="5">
+        <v>2</v>
+      </c>
+      <c r="D11" s="5">
+        <v>2</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>2</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>13</v>
+      </c>
+      <c r="C12" s="5">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5">
+        <v>2</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>2</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>12</v>
+      </c>
+      <c r="C13" s="5">
+        <v>2</v>
+      </c>
+      <c r="D13" s="5">
+        <v>2</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>2</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>9</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>7</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>7</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>7</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>12</v>
+      </c>
+      <c r="C15" s="5">
+        <v>2</v>
+      </c>
+      <c r="D15" s="5">
+        <v>2</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>2</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>1</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>9</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5">
+        <v>7</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>7</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>7</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>3</v>
+      </c>
+      <c r="D17" s="5">
+        <v>5</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>5</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>1</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3860,9 +6759,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3896,8 +6801,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3919,25 +6832,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5670288660758539</v>
+        <v>0.5335063790470352</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5004588272607521</v>
+        <v>0.5176560308032208</v>
       </c>
       <c r="D3" s="4">
-        <v>0.5537743825350011</v>
+        <v>0.495233680326739</v>
       </c>
       <c r="E3" s="4">
-        <v>86.51360544217692</v>
+        <v>86.91609977324264</v>
       </c>
       <c r="F3" s="4">
-        <v>82.38627889634454</v>
+        <v>80.97874720357898</v>
       </c>
       <c r="G3" s="5">
         <v>6</v>
@@ -3960,25 +6891,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.491239997047353</v>
+      </c>
+      <c r="O3" s="5">
+        <v>5</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4074054549218715</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4645829212624949</v>
+      </c>
+      <c r="R3" s="5">
+        <v>5</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5335063790470352</v>
+        <v>0.5670288660758539</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5176560308032208</v>
+        <v>0.5004588272607521</v>
       </c>
       <c r="D4" s="4">
-        <v>0.495233680326739</v>
+        <v>0.5537743825350011</v>
       </c>
       <c r="E4" s="4">
-        <v>86.91609977324264</v>
+        <v>86.51360544217692</v>
       </c>
       <c r="F4" s="4">
-        <v>80.97874720357898</v>
+        <v>82.38627889634454</v>
       </c>
       <c r="G4" s="5">
         <v>6</v>
@@ -4001,10 +6950,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.5004588272607521</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2864658678515563</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2638749948437453</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.644601303457037</v>
@@ -4042,9 +7009,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.644601303457037</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.9447587647534306</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4055,14 +7038,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4073,9 +7057,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4109,8 +7099,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4132,92 +7130,144 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.7127264597648187</v>
+        <v>0.7672166721354093</v>
       </c>
       <c r="C3" s="4">
-        <v>0.6313676127917631</v>
+        <v>0.7367522194843673</v>
       </c>
       <c r="D3" s="4">
-        <v>0.6518448450797601</v>
+        <v>0.6770067111979093</v>
       </c>
       <c r="E3" s="4">
-        <v>79.52947845805004</v>
+        <v>84.35941043083901</v>
       </c>
       <c r="F3" s="4">
-        <v>81.71327367636103</v>
+        <v>83.12826249067793</v>
       </c>
       <c r="G3" s="5">
         <v>6</v>
       </c>
       <c r="H3" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.6676741324843647</v>
+      </c>
+      <c r="O3" s="5">
+        <v>5</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5376239607812465</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.5947757923562449</v>
+      </c>
+      <c r="R3" s="5">
+        <v>5</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.7672166721354093</v>
+        <v>0.7127264597648187</v>
       </c>
       <c r="C4" s="4">
-        <v>0.7367522194843673</v>
+        <v>0.6313676127917631</v>
       </c>
       <c r="D4" s="4">
-        <v>0.6770067111979093</v>
+        <v>0.6518448450797601</v>
       </c>
       <c r="E4" s="4">
-        <v>84.35941043083901</v>
+        <v>79.52947845805004</v>
       </c>
       <c r="F4" s="4">
-        <v>83.12826249067793</v>
+        <v>81.71327367636103</v>
       </c>
       <c r="G4" s="5">
         <v>6</v>
       </c>
       <c r="H4" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>4</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.7127264597648187</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.6313676127917631</v>
+      </c>
+      <c r="R4" s="5">
+        <v>4</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>2.211256179939582</v>
@@ -4255,9 +7305,25 @@
       <c r="M5" s="5">
         <v>2</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>2.211256179939582</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>1.57286607937499</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4268,14 +7334,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4286,9 +7353,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4322,8 +7395,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4345,25 +7426,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4512671091788813</v>
+        <v>0.4230902446406333</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4575648606998357</v>
+        <v>0.4337398166111711</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4339419909947916</v>
+        <v>0.3809919956423092</v>
       </c>
       <c r="E3" s="4">
-        <v>88.12358276643991</v>
+        <v>89.00793650793651</v>
       </c>
       <c r="F3" s="4">
-        <v>86.78784489187183</v>
+        <v>87.34712900820291</v>
       </c>
       <c r="G3" s="5">
         <v>6</v>
@@ -4386,25 +7485,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.4337398166111711</v>
+      </c>
+      <c r="O3" s="5">
+        <v>5</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.218694730640154</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2496541904035394</v>
+      </c>
+      <c r="R3" s="5">
+        <v>5</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4230902446406333</v>
+        <v>0.4512671091788813</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4337398166111711</v>
+        <v>0.4575648606998357</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3809919956423092</v>
+        <v>0.4339419909947916</v>
       </c>
       <c r="E4" s="4">
-        <v>89.00793650793651</v>
+        <v>88.12358276643991</v>
       </c>
       <c r="F4" s="4">
-        <v>87.34712900820291</v>
+        <v>86.78784489187183</v>
       </c>
       <c r="G4" s="5">
         <v>6</v>
@@ -4427,10 +7544,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.4575648606998357</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2181698379082112</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2542465036647082</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.461951696771834</v>
@@ -4468,9 +7603,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.461951696771834</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4594065937110561</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4481,14 +7632,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4499,9 +7651,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4535,8 +7693,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4558,25 +7724,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.6030521649751867</v>
+        <v>0.5847720010178534</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4822452690637306</v>
+        <v>0.5524258815230609</v>
       </c>
       <c r="D3" s="4">
-        <v>0.5832732775443598</v>
+        <v>0.5509753727016099</v>
       </c>
       <c r="E3" s="4">
-        <v>83.76417233560089</v>
+        <v>82.3922902494331</v>
       </c>
       <c r="F3" s="4">
-        <v>84.0063385533181</v>
+        <v>83.67822520507052</v>
       </c>
       <c r="G3" s="5">
         <v>6</v>
@@ -4599,25 +7783,43 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.5524258815230609</v>
+      </c>
+      <c r="O3" s="5">
+        <v>5</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3598183780989548</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3929667103249949</v>
+      </c>
+      <c r="R3" s="5">
+        <v>5</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5847720010178534</v>
+        <v>0.6030521649751867</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5524258815230609</v>
+        <v>0.4822452690637306</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5509753727016099</v>
+        <v>0.5832732775443598</v>
       </c>
       <c r="E4" s="4">
-        <v>82.3922902494331</v>
+        <v>83.76417233560089</v>
       </c>
       <c r="F4" s="4">
-        <v>83.67822520507052</v>
+        <v>84.0063385533181</v>
       </c>
       <c r="G4" s="5">
         <v>6</v>
@@ -4640,10 +7842,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.4822452690637306</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3345858714843757</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2565347706875036</v>
+      </c>
+      <c r="R4" s="5">
+        <v>5</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.4052082466098028</v>
@@ -4681,9 +7901,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>3</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4052082466098028</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.5365608867222136</v>
+      </c>
+      <c r="R5" s="5">
+        <v>3</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4694,14 +7930,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4712,9 +7949,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4748,8 +7991,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4771,92 +8022,146 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4989385861787999</v>
+        <v>0.4727445943253485</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4989385861787999</v>
+        <v>0.4769351207198383</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4544252016776606</v>
+        <v>0.4460484686590481</v>
       </c>
       <c r="E3" s="4">
-        <v>88.70748299319729</v>
+        <v>87.74943310657598</v>
       </c>
       <c r="F3" s="4">
-        <v>89.01938851603285</v>
+        <v>82.56152125279421</v>
       </c>
       <c r="G3" s="5">
         <v>6</v>
       </c>
       <c r="H3" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.4769351207198383</v>
+      </c>
+      <c r="O3" s="5">
+        <v>5</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3282163172811636</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3888309490640086</v>
+      </c>
+      <c r="R3" s="5">
+        <v>5</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4727445943253485</v>
+        <v>0.4989385861787999</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4769351207198383</v>
+        <v>0.4989385861787999</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4460484686590481</v>
+        <v>0.4544252016776606</v>
       </c>
       <c r="E4" s="4">
-        <v>87.74943310657598</v>
+        <v>88.70748299319729</v>
       </c>
       <c r="F4" s="4">
-        <v>82.56152125279421</v>
+        <v>89.01938851603285</v>
       </c>
       <c r="G4" s="5">
         <v>6</v>
       </c>
       <c r="H4" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.4989385861787999</v>
+      </c>
+      <c r="O4" s="5">
+        <v>6</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2820508817100694</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2820508817100694</v>
+      </c>
+      <c r="R4" s="5">
+        <v>6</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.3998732150781308</v>
@@ -4894,9 +8199,25 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>2</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3998732150781308</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.7136169591046269</v>
+      </c>
+      <c r="R5" s="5">
+        <v>2</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4907,432 +8228,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.7103279699472679</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.7103279699472679</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.6944460328723894</v>
-      </c>
-      <c r="E3" s="4">
-        <v>86.22448979591837</v>
-      </c>
-      <c r="F3" s="4">
-        <v>87.57270693512309</v>
-      </c>
-      <c r="G3" s="5">
-        <v>6</v>
-      </c>
-      <c r="H3" s="5">
-        <v>6</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.6620017616691977</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.6620017616691977</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.6401892247868565</v>
-      </c>
-      <c r="E4" s="4">
-        <v>87.34693877551021</v>
-      </c>
-      <c r="F4" s="4">
-        <v>87.26510067114094</v>
-      </c>
-      <c r="G4" s="5">
-        <v>6</v>
-      </c>
-      <c r="H4" s="5">
-        <v>6</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.6545672069628257</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.8476553306344196</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.7908114537366648</v>
-      </c>
-      <c r="E5" s="4">
-        <v>82.88265306122449</v>
-      </c>
-      <c r="F5" s="4">
-        <v>69.17785234899328</v>
-      </c>
-      <c r="G5" s="5">
-        <v>4</v>
-      </c>
-      <c r="H5" s="5">
-        <v>3</v>
-      </c>
-      <c r="I5" s="5">
-        <v>1</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>1.039465770983081</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.7350286731250151</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1.033405647539477</v>
-      </c>
-      <c r="E3" s="4">
-        <v>81.64965986394557</v>
-      </c>
-      <c r="F3" s="4">
-        <v>82.99589858314683</v>
-      </c>
-      <c r="G3" s="5">
-        <v>6</v>
-      </c>
-      <c r="H3" s="5">
-        <v>4</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>2</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>1</v>
-      </c>
-      <c r="M3" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.9800526006119696</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.9800526006119696</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.9507936341660468</v>
-      </c>
-      <c r="E4" s="4">
-        <v>83.29931972789116</v>
-      </c>
-      <c r="F4" s="4">
-        <v>85.72147651006711</v>
-      </c>
-      <c r="G4" s="5">
-        <v>6</v>
-      </c>
-      <c r="H4" s="5">
-        <v>6</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.9290913678515693</v>
-      </c>
-      <c r="C5" s="4">
-        <v>1.115376267454432</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.9866067506182929</v>
-      </c>
-      <c r="E5" s="4">
-        <v>79.37074829931974</v>
-      </c>
-      <c r="F5" s="4">
-        <v>77.20357941834452</v>
-      </c>
-      <c r="G5" s="5">
-        <v>4</v>
-      </c>
-      <c r="H5" s="5">
-        <v>3</v>
-      </c>
-      <c r="I5" s="5">
-        <v>1</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/FesterEdge2017.xlsx
+++ b/public/downloads/FesterEdge2017.xlsx
@@ -1557,16 +1557,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.6620017616691977</v>
+        <v>0.5589261524171434</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4121541910309108</v>
+        <v>0.3969912058521648</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4121541910309108</v>
+        <v>0.3969912058521648</v>
       </c>
       <c r="R3" s="5">
         <v>6</v>
@@ -1616,16 +1616,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.6152980409050129</v>
+        <v>0.5540087111568965</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
       </c>
       <c r="P4" s="4">
-        <v>0.499095761554517</v>
+        <v>0.494380718070876</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.499095761554517</v>
+        <v>0.494380718070876</v>
       </c>
       <c r="R4" s="5">
         <v>6</v>
@@ -1855,7 +1855,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.9800526006119696</v>
+        <v>1.038378641601554</v>
       </c>
       <c r="O3" s="5">
         <v>6</v>
@@ -1914,7 +1914,7 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>0.9941847399101675</v>
+        <v>0.5681655452539189</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
@@ -1923,7 +1923,7 @@
         <v>0.5591353421354105</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.616625173274997</v>
+        <v>0.5314213343437473</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
@@ -2153,7 +2153,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.4827330838479668</v>
+        <v>0.277188489752433</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
@@ -2162,7 +2162,7 @@
         <v>0.3710834786934782</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.414141713907527</v>
+        <v>0.3730327950884202</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -2212,7 +2212,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2863111647192282</v>
+        <v>0.1660970562863895</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
@@ -2221,7 +2221,7 @@
         <v>0.3022738045837818</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2469963176922603</v>
+        <v>0.2229534960056926</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
@@ -2451,7 +2451,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.5409250937880756</v>
+        <v>0.3202058866943389</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
@@ -2460,7 +2460,7 @@
         <v>0.308452207851559</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3354862415749949</v>
+        <v>0.2913424001562476</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -2510,16 +2510,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.4749518539941505</v>
+        <v>0.4009514761816604</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2338310700520841</v>
+        <v>0.2226403104427087</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1964224660000036</v>
+        <v>0.1681934789062552</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
@@ -2749,16 +2749,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2844169818343403</v>
+        <v>0.1144179895843536</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2665810137838491</v>
+        <v>0.2260750919661424</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2955936634499949</v>
+        <v>0.2615938649999975</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -2808,16 +2808,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2516220238244727</v>
+        <v>0.2344162509729131</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
       </c>
       <c r="P4" s="4">
-        <v>0.185332026269532</v>
+        <v>0.1822813992643167</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1762186085781286</v>
+        <v>0.1691167016015584</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
@@ -3047,7 +3047,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1800077639998676</v>
+        <v>-0.003022234109494093</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
@@ -3056,7 +3056,7 @@
         <v>0.3848122745833298</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4134769642312449</v>
+        <v>0.3768709646093725</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -3106,16 +3106,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2563419487512306</v>
+        <v>0.2023594425012334</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3109662832682299</v>
+        <v>0.2980523750130146</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2422940480312537</v>
+        <v>0.2160008568749959</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
@@ -3639,7 +3639,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.01870558490176109</v>
+        <v>0.008879702945421286</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
@@ -3648,7 +3648,7 @@
         <v>0.2432301996133977</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2844956323941505</v>
+        <v>0.2825304560028826</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -3698,16 +3698,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.02048430705448041</v>
+        <v>0.1202838535554065</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2454653998629838</v>
+        <v>0.2121988843626751</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1494264302515015</v>
+        <v>0.1294665209513162</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
@@ -4492,10 +4492,10 @@
         <v>0.4213520719042947</v>
       </c>
       <c r="I3" s="4">
-        <v>0.4609839258365052</v>
+        <v>0.4454595683768711</v>
       </c>
       <c r="J3" s="4">
-        <v>0.3813883386514263</v>
+        <v>0.3857040725610332</v>
       </c>
       <c r="K3" s="4">
         <v>86.05867346938776</v>
@@ -4542,10 +4542,10 @@
         <v>1.02169545268967</v>
       </c>
       <c r="I4" s="4">
-        <v>0.7072215492323266</v>
+        <v>0.7037012642651405</v>
       </c>
       <c r="J4" s="4">
-        <v>1.107532532265658</v>
+        <v>1.103132176056675</v>
       </c>
       <c r="K4" s="4">
         <v>82.59778911564626</v>
@@ -4589,13 +4589,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.2793121373985954</v>
+        <v>0.271324958420692</v>
       </c>
       <c r="I5" s="4">
-        <v>0.2998248654980312</v>
+        <v>0.2854858301144532</v>
       </c>
       <c r="J5" s="4">
-        <v>0.2592520805780836</v>
+        <v>0.2410812190386338</v>
       </c>
       <c r="K5" s="4">
         <v>88.10799319727892</v>
@@ -4639,13 +4639,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.3617036552461997</v>
+        <v>0.3549825827169002</v>
       </c>
       <c r="I6" s="4">
-        <v>0.3736300050176257</v>
+        <v>0.3383995712808445</v>
       </c>
       <c r="J6" s="4">
-        <v>0.329733471805956</v>
+        <v>0.3426591303398894</v>
       </c>
       <c r="K6" s="4">
         <v>82.98469387755102</v>
@@ -4689,13 +4689,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.3288185033912451</v>
+        <v>0.3147255612841775</v>
       </c>
       <c r="I7" s="4">
-        <v>0.3895149195222857</v>
+        <v>0.3571557176326792</v>
       </c>
       <c r="J7" s="4">
-        <v>0.3303927687636825</v>
+        <v>0.3135329735130306</v>
       </c>
       <c r="K7" s="4">
         <v>87.31930272108846</v>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.5053605339602418</v>
+        <v>0.4979062732118467</v>
       </c>
       <c r="I8" s="4">
-        <v>0.534031047161055</v>
+        <v>0.5260798356961003</v>
       </c>
       <c r="J8" s="4">
-        <v>0.5242694239394903</v>
+        <v>0.5113849727829834</v>
       </c>
       <c r="K8" s="4">
         <v>85.80994897959184</v>
@@ -4792,10 +4792,10 @@
         <v>0.6626539550683574</v>
       </c>
       <c r="I9" s="4">
-        <v>0.7114671732580901</v>
+        <v>0.6810372307826437</v>
       </c>
       <c r="J9" s="4">
-        <v>0.6483672581574993</v>
+        <v>0.6504403404411292</v>
       </c>
       <c r="K9" s="4">
         <v>81.69855442176872</v>
@@ -4842,10 +4842,10 @@
         <v>0.3605103151597085</v>
       </c>
       <c r="I10" s="4">
-        <v>0.3768156935026626</v>
+        <v>0.3517573317697109</v>
       </c>
       <c r="J10" s="4">
-        <v>0.3359523721648084</v>
+        <v>0.3359523721648085</v>
       </c>
       <c r="K10" s="4">
         <v>88.28231292517007</v>
@@ -4889,13 +4889,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.3409317259765629</v>
+        <v>0.3367351911230472</v>
       </c>
       <c r="I11" s="4">
-        <v>0.3578022525939142</v>
+        <v>0.3276469073803743</v>
       </c>
       <c r="J11" s="4">
-        <v>0.2947778095413227</v>
+        <v>0.3075532504832452</v>
       </c>
       <c r="K11" s="4">
         <v>85.68239795918367</v>
@@ -4939,13 +4939,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>0.2440202732573241</v>
+        <v>0.2276865674487283</v>
       </c>
       <c r="I12" s="4">
-        <v>0.2417824441282042</v>
+        <v>0.2259740958872166</v>
       </c>
       <c r="J12" s="4">
-        <v>0.2022485675677047</v>
+        <v>0.179715010998919</v>
       </c>
       <c r="K12" s="4">
         <v>90.74404761904761</v>
@@ -4989,13 +4989,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.3686710600830082</v>
+        <v>0.3638283444873025</v>
       </c>
       <c r="I13" s="4">
-        <v>0.3427578574650283</v>
+        <v>0.3165498613074741</v>
       </c>
       <c r="J13" s="4">
-        <v>0.2927442538093586</v>
+        <v>0.2892282639724755</v>
       </c>
       <c r="K13" s="4">
         <v>85.58248299319727</v>
@@ -5089,13 +5089,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.3002459017011899</v>
+        <v>0.2877709583885741</v>
       </c>
       <c r="I15" s="4">
-        <v>0.2286615477628555</v>
+        <v>0.2195260953914167</v>
       </c>
       <c r="J15" s="4">
-        <v>0.2833176093083973</v>
+        <v>0.2910679165442434</v>
       </c>
       <c r="K15" s="4">
         <v>90.17431972789115</v>
@@ -6892,7 +6892,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.491239997047353</v>
+        <v>0.3783027723754913</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
@@ -6901,7 +6901,7 @@
         <v>0.4074054549218715</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4645829212624949</v>
+        <v>0.4419954763281225</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -6951,7 +6951,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.5004588272607521</v>
+        <v>0.4271037624170049</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
@@ -6960,7 +6960,7 @@
         <v>0.2864658678515563</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2638749948437453</v>
+        <v>0.2492039818749959</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
@@ -7190,7 +7190,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.6676741324843647</v>
+        <v>0.632471282812503</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
@@ -7199,7 +7199,7 @@
         <v>0.5376239607812465</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5947757923562449</v>
+        <v>0.5877352224218726</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -7486,16 +7486,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.4337398166111711</v>
+        <v>0.2883729242955724</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
       </c>
       <c r="P3" s="4">
-        <v>0.218694730640154</v>
+        <v>0.1973955866990783</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2496541904035394</v>
+        <v>0.2205808119404196</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -7545,7 +7545,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.4575648606998357</v>
+        <v>0.4986054283707517</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
@@ -7554,7 +7554,7 @@
         <v>0.2181698379082112</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2542465036647082</v>
+        <v>0.2460383901305249</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
@@ -7784,7 +7784,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.5524258815230609</v>
+        <v>0.3168873384918243</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
@@ -7793,7 +7793,7 @@
         <v>0.3598183780989548</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3929667103249949</v>
+        <v>0.3458590017187476</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -7843,16 +7843,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.4822452690637306</v>
+        <v>0.3673253339856046</v>
       </c>
       <c r="O4" s="5">
         <v>5</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3345858714843757</v>
+        <v>0.3166630114062438</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2565347706875036</v>
+        <v>0.2120433515781201</v>
       </c>
       <c r="R4" s="5">
         <v>5</v>
@@ -8082,16 +8082,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.4769351207198383</v>
+        <v>0.2314662531341583</v>
       </c>
       <c r="O3" s="5">
         <v>5</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3282163172811636</v>
+        <v>0.319835264492184</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3888309490640086</v>
+        <v>0.3397371755468725</v>
       </c>
       <c r="R3" s="5">
         <v>5</v>
@@ -8141,16 +8141,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.4989385861787999</v>
+        <v>0.3640602241735849</v>
       </c>
       <c r="O4" s="5">
         <v>6</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2820508817100694</v>
+        <v>0.2528507555468688</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2820508817100694</v>
+        <v>0.2528507555468688</v>
       </c>
       <c r="R4" s="5">
         <v>6</v>
